--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/CstpTrdMatchInfo.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/CstpTrdMatchInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\2.1.2\2.1.2\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZNEW\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>成交编号</t>
   </si>
@@ -56,9 +56,6 @@
     <t>证券账户</t>
   </si>
   <si>
-    <t>委托编号</t>
-  </si>
-  <si>
     <t>投资经理</t>
   </si>
   <si>
@@ -104,6 +101,18 @@
   </si>
   <si>
     <t>实际占款天数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易手续费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算手续费</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -111,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +131,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -146,8 +163,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -452,30 +470,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="17" max="17" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>15</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -493,28 +511,28 @@
         <v>4</v>
       </c>
       <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
         <v>16</v>
-      </c>
-      <c r="M1" t="s">
-        <v>17</v>
       </c>
       <c r="N1" t="s">
         <v>5</v>
       </c>
       <c r="O1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P1" t="s">
         <v>6</v>
       </c>
       <c r="Q1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
         <v>7</v>
       </c>
       <c r="S1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>8</v>
@@ -526,22 +544,28 @@
         <v>10</v>
       </c>
       <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
